--- a/app/assets/data-import-samples/invoice/invoice.xlsx
+++ b/app/assets/data-import-samples/invoice/invoice.xlsx
@@ -140,9 +140,6 @@
     <t>(Only No)</t>
   </si>
   <si>
-    <t>(Material Advance/Interest Recovery/Mob Advance Adjustment/Erection Advance/Other Deductions)</t>
-  </si>
-  <si>
     <t>Credit Invoice Amount</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>ORG ID</t>
+  </si>
+  <si>
+    <t>(Material Advance/Interest Recovery/Mob Advance Adjustment/Erection Advance/LD Advance Adjustment/Other Deductions)</t>
   </si>
 </sst>
 </file>
@@ -555,7 +555,7 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -579,7 +579,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
@@ -666,16 +666,16 @@
         <v>35</v>
       </c>
       <c r="AL1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
@@ -729,7 +729,7 @@
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>

--- a/app/assets/data-import-samples/invoice/invoice.xlsx
+++ b/app/assets/data-import-samples/invoice/invoice.xlsx
@@ -24,115 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
-  <si>
-    <t>Invoice Date</t>
-  </si>
-  <si>
-    <t>Invoice No</t>
-  </si>
-  <si>
-    <t>(DD-MM-YYYY)</t>
-  </si>
-  <si>
-    <t>Creation Date</t>
-  </si>
-  <si>
-    <t>Invoice Amount</t>
-  </si>
-  <si>
-    <t>Amount Paid</t>
-  </si>
-  <si>
-    <t>Invoice Category</t>
-  </si>
-  <si>
-    <t>Invoice Type</t>
-  </si>
-  <si>
-    <t>OU Name</t>
-  </si>
-  <si>
-    <t>Vendor ID</t>
-  </si>
-  <si>
-    <t>Vendor Code</t>
-  </si>
-  <si>
-    <t>Vendor Name</t>
-  </si>
-  <si>
-    <t>Vendor Site Code</t>
-  </si>
-  <si>
-    <t>Voucher</t>
-  </si>
-  <si>
-    <t>Invoice Description</t>
-  </si>
-  <si>
-    <t>GL Date</t>
-  </si>
-  <si>
-    <t>Payment Terms</t>
-  </si>
-  <si>
-    <t>Payment Status Flag</t>
-  </si>
-  <si>
-    <t>Payment Status</t>
-  </si>
-  <si>
-    <t>Validation Status</t>
-  </si>
-  <si>
-    <t>Accounted Status</t>
-  </si>
-  <si>
-    <t>Approval Status</t>
-  </si>
-  <si>
-    <t>Term Date</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Balance</t>
-  </si>
-  <si>
-    <t>Last Payment Date</t>
-  </si>
-  <si>
-    <t>Attribute Category</t>
-  </si>
-  <si>
-    <t>Contract No</t>
-  </si>
-  <si>
-    <t>Scheme Code</t>
-  </si>
-  <si>
-    <t>GST Tax</t>
-  </si>
-  <si>
-    <t>LIN Tax</t>
-  </si>
-  <si>
-    <t>TDS GST Amount</t>
-  </si>
-  <si>
-    <t>TDS IT Amount</t>
-  </si>
-  <si>
-    <t>Contract Description</t>
-  </si>
-  <si>
-    <t>BG Advance Type</t>
-  </si>
-  <si>
-    <t>Credit Invoice No</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
   <si>
     <t>(Prepayment/Credit/Standard)</t>
   </si>
@@ -140,31 +32,139 @@
     <t>(Only No)</t>
   </si>
   <si>
-    <t>Credit Invoice Amount</t>
-  </si>
-  <si>
-    <t>PO Header ID</t>
-  </si>
-  <si>
-    <t>Project ID</t>
-  </si>
-  <si>
-    <t>Sysdate</t>
-  </si>
-  <si>
-    <t>Invoice ID</t>
-  </si>
-  <si>
-    <t>ORG ID</t>
-  </si>
-  <si>
-    <t>(Material Advance/Interest Recovery/Mob Advance Adjustment/Erection Advance/LD Advance Adjustment/Other Deductions)</t>
+    <t>INVOICE_ID</t>
+  </si>
+  <si>
+    <t>INVOICE_NUM</t>
+  </si>
+  <si>
+    <t>INVOICE_DATE</t>
+  </si>
+  <si>
+    <t>CREATION_DATE</t>
+  </si>
+  <si>
+    <t>INVOICE_AMOUNT</t>
+  </si>
+  <si>
+    <t>AMOUNT_PAID</t>
+  </si>
+  <si>
+    <t>INVOICE_CATEGEORY</t>
+  </si>
+  <si>
+    <t>INVOICE_TYPE</t>
+  </si>
+  <si>
+    <t>ORG_ID</t>
+  </si>
+  <si>
+    <t>OU_NAME</t>
+  </si>
+  <si>
+    <t>VENDOR_ID</t>
+  </si>
+  <si>
+    <t>VENDOR_CODE</t>
+  </si>
+  <si>
+    <t>VENDOR_NAME</t>
+  </si>
+  <si>
+    <t>VENDOR_SITE_CODE</t>
+  </si>
+  <si>
+    <t>VOUCHER</t>
+  </si>
+  <si>
+    <t>INVOICE_DESCRIPTION</t>
+  </si>
+  <si>
+    <t>GL_DATE</t>
+  </si>
+  <si>
+    <t>PAYMENT_TERMS</t>
+  </si>
+  <si>
+    <t>PAYMENT_STATUS_FLAG</t>
+  </si>
+  <si>
+    <t>PAYMENT_STATUS</t>
+  </si>
+  <si>
+    <t>VALIDATION_STATUS</t>
+  </si>
+  <si>
+    <t>ACCOUNTED_STATUS</t>
+  </si>
+  <si>
+    <t>APPROVAL_STATUS</t>
+  </si>
+  <si>
+    <t>TERM_DATE</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>BALANCE</t>
+  </si>
+  <si>
+    <t>LAST_PAYMENT_DATE</t>
+  </si>
+  <si>
+    <t>ATTRIBUTE_CATEGORY</t>
+  </si>
+  <si>
+    <t>CONTRACT_NUMBER</t>
+  </si>
+  <si>
+    <t>SCHEME_CODE</t>
+  </si>
+  <si>
+    <t>GST_TAX</t>
+  </si>
+  <si>
+    <t>LIN_TAX</t>
+  </si>
+  <si>
+    <t>TDS_GST_AMT</t>
+  </si>
+  <si>
+    <t>TDS_IT_AMT</t>
+  </si>
+  <si>
+    <t>CONTRACT_DESCRIPTION</t>
+  </si>
+  <si>
+    <t>BG_ADVANCE_TYPE</t>
+  </si>
+  <si>
+    <t>CREDIT_INVOICE_AMT</t>
+  </si>
+  <si>
+    <t>PO_HEADER_ID</t>
+  </si>
+  <si>
+    <t>PROJECT_ID</t>
+  </si>
+  <si>
+    <t>SYSDATE</t>
+  </si>
+  <si>
+    <t>(Material Advance/Interest Recovery/Mob Advance Adjustment/Erection Advance/Other Deductions)</t>
+  </si>
+  <si>
+    <t>(DD/MM/YYYY)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -226,12 +226,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -517,153 +535,156 @@
   <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="21" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="14" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="93.42578125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>7</v>
+      </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>38</v>
@@ -674,24 +695,24 @@
       <c r="AN1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="C2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -701,8 +722,8 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
-      <c r="Q2" s="2" t="s">
-        <v>2</v>
+      <c r="Q2" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
@@ -710,17 +731,17 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-      <c r="X2" s="2" t="s">
-        <v>2</v>
+      <c r="X2" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
-      <c r="AA2" s="2" t="s">
-        <v>2</v>
+      <c r="AA2" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
@@ -729,14 +750,14 @@
       <c r="AH2" s="2"/>
       <c r="AI2" s="2"/>
       <c r="AJ2" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
       <c r="AM2" s="2"/>
       <c r="AN2" s="2"/>
-      <c r="AO2" s="2" t="s">
-        <v>2</v>
+      <c r="AO2" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/app/assets/data-import-samples/invoice/invoice.xlsx
+++ b/app/assets/data-import-samples/invoice/invoice.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>(Prepayment/Credit/Standard)</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>(DD/MM/YYYY)</t>
+  </si>
+  <si>
+    <t>CREDIT_INVOICE_NO</t>
   </si>
 </sst>
 </file>
@@ -684,7 +687,7 @@
         <v>37</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AL1" s="1" t="s">
         <v>38</v>

--- a/app/assets/data-import-samples/invoice/invoice.xlsx
+++ b/app/assets/data-import-samples/invoice/invoice.xlsx
@@ -158,7 +158,7 @@
     <t>(DD/MM/YYYY)</t>
   </si>
   <si>
-    <t>CREDIT_INVOICE_NO</t>
+    <t>CREDIT_INVOICE_NUM</t>
   </si>
 </sst>
 </file>
